--- a/artfynd/A 56368-2022 artfynd.xlsx
+++ b/artfynd/A 56368-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56368-2022 artfynd.xlsx
+++ b/artfynd/A 56368-2022 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88510821</v>
+        <v>89557335</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>735</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rörtjärnen, Jmt</t>
+          <t>Tjaajatjaeltjie, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396966.1306848881</v>
+        <v>396973</v>
       </c>
       <c r="R2" t="n">
-        <v>7078780.822365844</v>
+        <v>7078778</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,66 +756,70 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Björkstubbe</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89557335</v>
+        <v>88510821</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjaajatjaeltjie, Jmt</t>
+          <t>Rörtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396973.1159762506</v>
+        <v>396966</v>
       </c>
       <c r="R3" t="n">
-        <v>7078777.941788577</v>
+        <v>7078781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,44 +862,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Björkstubbe</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>89557364</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -948,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>396870.9049558246</v>
+        <v>396871</v>
       </c>
       <c r="R4" t="n">
-        <v>7079114.918660825</v>
+        <v>7079115</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +946,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89557358</v>
+        <v>89557336</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397140.9617483697</v>
+        <v>397371</v>
       </c>
       <c r="R5" t="n">
-        <v>7078984.990259781</v>
+        <v>7079260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,19 +1047,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,37 +1080,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89557363</v>
+        <v>89557361</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397217.1697817852</v>
+        <v>397426</v>
       </c>
       <c r="R6" t="n">
-        <v>7078717.800637193</v>
+        <v>7079329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,19 +1148,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89557673</v>
+        <v>89557329</v>
       </c>
       <c r="B7" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220686</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396757.2116797691</v>
+        <v>396951</v>
       </c>
       <c r="R7" t="n">
-        <v>7079276.836674449</v>
+        <v>7078804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,19 +1249,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89557355</v>
+        <v>89557321</v>
       </c>
       <c r="B8" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397156.2014463674</v>
+        <v>397374</v>
       </c>
       <c r="R8" t="n">
-        <v>7079045.027627605</v>
+        <v>7079251</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,19 +1350,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,37 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89557357</v>
+        <v>89557656</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1528,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396904.132459689</v>
+        <v>396824</v>
       </c>
       <c r="R9" t="n">
-        <v>7078941.055474633</v>
+        <v>7079383</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,19 +1451,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,37 +1484,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89557361</v>
+        <v>89557354</v>
       </c>
       <c r="B10" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>397426.0824903461</v>
+        <v>397441</v>
       </c>
       <c r="R10" t="n">
-        <v>7079329.145109615</v>
+        <v>7079337</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,19 +1552,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,19 +1585,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89557354</v>
+        <v>89557358</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1760,10 +1620,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>397440.9401537369</v>
+        <v>397141</v>
       </c>
       <c r="R11" t="n">
-        <v>7079337.05448933</v>
+        <v>7078985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,19 +1653,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,37 +1686,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89557320</v>
+        <v>89557638</v>
       </c>
       <c r="B12" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1876,10 +1721,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>397449.9710449383</v>
+        <v>396756</v>
       </c>
       <c r="R12" t="n">
-        <v>7079356.199739774</v>
+        <v>7079276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,19 +1754,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,37 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89557329</v>
+        <v>89557320</v>
       </c>
       <c r="B13" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>396950.9569315949</v>
+        <v>397450</v>
       </c>
       <c r="R13" t="n">
-        <v>7078803.857319436</v>
+        <v>7079356</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,19 +1855,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,15 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89557343</v>
+        <v>89557330</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,21 +1899,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2108,10 +1923,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>397288.9666188369</v>
+        <v>397421</v>
       </c>
       <c r="R14" t="n">
-        <v>7079221.84301562</v>
+        <v>7079303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,19 +1956,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,15 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89557336</v>
+        <v>89557357</v>
       </c>
       <c r="B15" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,21 +2000,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2224,10 +2024,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>397371.1701968185</v>
+        <v>396904</v>
       </c>
       <c r="R15" t="n">
-        <v>7079259.804587347</v>
+        <v>7078941</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,19 +2057,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,37 +2090,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89557359</v>
+        <v>89557350</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2340,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396877.113614419</v>
+        <v>397215</v>
       </c>
       <c r="R16" t="n">
-        <v>7079021.038915424</v>
+        <v>7078638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,19 +2158,14 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,15 +2196,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89557337</v>
+        <v>89557355</v>
       </c>
       <c r="B17" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,21 +2207,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229748</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2456,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397366.068834592</v>
+        <v>397156</v>
       </c>
       <c r="R17" t="n">
-        <v>7079266.156999105</v>
+        <v>7079045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,21 +2264,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2512,11 +2277,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2537,37 +2297,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89557330</v>
+        <v>89557673</v>
       </c>
       <c r="B18" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>220686</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2577,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397420.7981228495</v>
+        <v>396757</v>
       </c>
       <c r="R18" t="n">
-        <v>7079302.80810794</v>
+        <v>7079277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,19 +2365,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,15 +2398,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89557321</v>
+        <v>89557359</v>
       </c>
       <c r="B19" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2669,21 +2409,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2693,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>397373.9753185908</v>
+        <v>396877</v>
       </c>
       <c r="R19" t="n">
-        <v>7079250.876195003</v>
+        <v>7079021</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,19 +2466,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,37 +2499,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89557638</v>
+        <v>89557363</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2809,10 +2534,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>396755.8568351881</v>
+        <v>397217</v>
       </c>
       <c r="R20" t="n">
-        <v>7079275.997539036</v>
+        <v>7078718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2842,19 +2567,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2885,37 +2600,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89557350</v>
+        <v>89557337</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2925,10 +2635,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397214.9971839766</v>
+        <v>397366</v>
       </c>
       <c r="R21" t="n">
-        <v>7078637.884501265</v>
+        <v>7079266</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,26 +2668,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2986,6 +2681,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 56368-2022 artfynd.xlsx
+++ b/artfynd/A 56368-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557335</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88510821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557364</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557336</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557361</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557329</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557656</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557354</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557358</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557638</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557320</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1986,6 +2051,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557330</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,6 +2157,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557357</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557350</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557355</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557673</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2496,6 +2586,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557359</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557363</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2703,8 +2803,35 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89557337</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>